--- a/health_check_logger - Test_lab/host_info.xlsx
+++ b/health_check_logger - Test_lab/host_info.xlsx
@@ -5,25 +5,42 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\OneDrive\Documents\Meralco-SR-MPLS\Automation\health_check_logger\health_check_logger - Test_lab\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cisco-my.sharepoint.com/personal/rbinguna_cisco_com/Documents/Documents/GitHub/network-automation-lab/health_check_logger - Test_lab/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E896190-A4D8-4136-AC39-6E8DD4B58859}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="86" documentId="13_ncr:1_{1E896190-A4D8-4136-AC39-6E8DD4B58859}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8AFCD360-F709-4681-921F-AB4127666739}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Device_Inventory" sheetId="1" r:id="rId1"/>
+    <sheet name="ASR9K and SW93" sheetId="2" r:id="rId2"/>
+    <sheet name="ASR903" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet3" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet4" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Device_Inventory!$A$1:$E$23</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="338">
   <si>
     <t>Hostname</t>
   </si>
@@ -203,13 +220,847 @@
   </si>
   <si>
     <t>Switch2</t>
+  </si>
+  <si>
+    <t>PDCPASR9K</t>
+  </si>
+  <si>
+    <t>ASR9910</t>
+  </si>
+  <si>
+    <t>PDC – Meralco MOC Data Center</t>
+  </si>
+  <si>
+    <t>10.228.203.1</t>
+  </si>
+  <si>
+    <t>VPN_OT_Mgt</t>
+  </si>
+  <si>
+    <t>SDCPASR9K</t>
+  </si>
+  <si>
+    <t>SDC – Meralco DRF Site (Balintawak Sector)</t>
+  </si>
+  <si>
+    <t>10.228.203.2</t>
+  </si>
+  <si>
+    <t>ALBPASR9K</t>
+  </si>
+  <si>
+    <t>Paranaque Sector (Alabang)</t>
+  </si>
+  <si>
+    <t>10.228.203.3</t>
+  </si>
+  <si>
+    <t>SPBPASR9K</t>
+  </si>
+  <si>
+    <t>San Pablo Sector</t>
+  </si>
+  <si>
+    <t>10.228.203.4</t>
+  </si>
+  <si>
+    <t>SRSPASR9K</t>
+  </si>
+  <si>
+    <t>Sta. Rosa Sector</t>
+  </si>
+  <si>
+    <t>10.228.203.5</t>
+  </si>
+  <si>
+    <t>RZLPASR9K</t>
+  </si>
+  <si>
+    <t>Rizal Sector</t>
+  </si>
+  <si>
+    <t>10.228.203.6</t>
+  </si>
+  <si>
+    <t>MNLPASR9K</t>
+  </si>
+  <si>
+    <t>Manila Sector</t>
+  </si>
+  <si>
+    <t>10.228.203.7</t>
+  </si>
+  <si>
+    <t>CVTPASR9K</t>
+  </si>
+  <si>
+    <t>Cavite Sector (also Dasmarinas Sector)</t>
+  </si>
+  <si>
+    <t>10.228.203.8</t>
+  </si>
+  <si>
+    <t>PDLPASR9K</t>
+  </si>
+  <si>
+    <t>Plaridel Sector</t>
+  </si>
+  <si>
+    <t>10.228.203.9</t>
+  </si>
+  <si>
+    <t>VLZPASR9K</t>
+  </si>
+  <si>
+    <t>Valenzuela Sector</t>
+  </si>
+  <si>
+    <t>10.228.203.10</t>
+  </si>
+  <si>
+    <t>PSGPASR9K</t>
+  </si>
+  <si>
+    <t>Pasig Sector</t>
+  </si>
+  <si>
+    <t>10.228.203.11</t>
+  </si>
+  <si>
+    <t>KMGPASR9K</t>
+  </si>
+  <si>
+    <t>Kamagong Substation (Formerly Rockwell Substation)</t>
+  </si>
+  <si>
+    <t>10.228.203.12</t>
+  </si>
+  <si>
+    <t>DHTPASR9K</t>
+  </si>
+  <si>
+    <t>Duhat Substation</t>
+  </si>
+  <si>
+    <t>10.228.203.13</t>
+  </si>
+  <si>
+    <t>MKNPASR9K</t>
+  </si>
+  <si>
+    <t>Marikina Substation</t>
+  </si>
+  <si>
+    <t>10.228.203.14</t>
+  </si>
+  <si>
+    <t>MTPPASR9K</t>
+  </si>
+  <si>
+    <t>Metpark Substation</t>
+  </si>
+  <si>
+    <t>10.228.203.15</t>
+  </si>
+  <si>
+    <t>CLRPASR9K</t>
+  </si>
+  <si>
+    <t>Calmelray Industrial Park Substation</t>
+  </si>
+  <si>
+    <t>10.228.203.16</t>
+  </si>
+  <si>
+    <t>PDCP9300SW</t>
+  </si>
+  <si>
+    <t>Catalyst 9300 </t>
+  </si>
+  <si>
+    <t>10.228.203.51</t>
+  </si>
+  <si>
+    <t>SDCP9300SW</t>
+  </si>
+  <si>
+    <t>10.228.203.52</t>
+  </si>
+  <si>
+    <t>DHTP9300SW</t>
+  </si>
+  <si>
+    <t>10.228.203.53</t>
+  </si>
+  <si>
+    <t>SRSP9300SW</t>
+  </si>
+  <si>
+    <t>10.228.203.54</t>
+  </si>
+  <si>
+    <t>ALBP9300SW</t>
+  </si>
+  <si>
+    <t>10.228.203.55</t>
+  </si>
+  <si>
+    <t>CVTP9300SW</t>
+  </si>
+  <si>
+    <t>10.228.203.56</t>
+  </si>
+  <si>
+    <t>SPBP9300SW</t>
+  </si>
+  <si>
+    <t>10.228.203.57</t>
+  </si>
+  <si>
+    <t>BWGP9300SW</t>
+  </si>
+  <si>
+    <t>10.228.203.58</t>
+  </si>
+  <si>
+    <t>CLBPNKSW</t>
+  </si>
+  <si>
+    <t>Nexus 9K Switch</t>
+  </si>
+  <si>
+    <t>10.228.203.59</t>
+  </si>
+  <si>
+    <t>Device-type</t>
+  </si>
+  <si>
+    <t>Site-Name</t>
+  </si>
+  <si>
+    <t>Loopback 50</t>
+  </si>
+  <si>
+    <t>VRF Management Name</t>
+  </si>
+  <si>
+    <t>Interface</t>
+  </si>
+  <si>
+    <t>10.240.8.1</t>
+  </si>
+  <si>
+    <t>AMADSUBPE01</t>
+  </si>
+  <si>
+    <t>Loopback0</t>
+  </si>
+  <si>
+    <t>10.240.8.2</t>
+  </si>
+  <si>
+    <t>BLWKSUBPE01</t>
+  </si>
+  <si>
+    <t>10.240.8.3</t>
+  </si>
+  <si>
+    <t>CALNSUBPE01</t>
+  </si>
+  <si>
+    <t>10.240.8.4</t>
+  </si>
+  <si>
+    <t>DLRSSUBPE01</t>
+  </si>
+  <si>
+    <t>10.240.8.5</t>
+  </si>
+  <si>
+    <t>DHATSUBPE01</t>
+  </si>
+  <si>
+    <t>10.240.8.6</t>
+  </si>
+  <si>
+    <t>GARDSUBPE01</t>
+  </si>
+  <si>
+    <t>10.240.8.7</t>
+  </si>
+  <si>
+    <t>MLLSSUBPE01</t>
+  </si>
+  <si>
+    <t>10.240.8.8</t>
+  </si>
+  <si>
+    <t>NPRTSUBPE01</t>
+  </si>
+  <si>
+    <t>10.240.8.9</t>
+  </si>
+  <si>
+    <t>PACOSUBPE01</t>
+  </si>
+  <si>
+    <t>10.240.8.10</t>
+  </si>
+  <si>
+    <t>STAMSUBPE01</t>
+  </si>
+  <si>
+    <t>10.240.8.11</t>
+  </si>
+  <si>
+    <t>STRASUBPE01</t>
+  </si>
+  <si>
+    <t>10.240.8.12</t>
+  </si>
+  <si>
+    <t>TGENSUBPE01</t>
+  </si>
+  <si>
+    <t>10.240.8.13</t>
+  </si>
+  <si>
+    <t>ZPTESUBPE01</t>
+  </si>
+  <si>
+    <t>10.240.8.14</t>
+  </si>
+  <si>
+    <t>STRASECPE01</t>
+  </si>
+  <si>
+    <t>10.240.8.15</t>
+  </si>
+  <si>
+    <t>BLGTRPTPE01</t>
+  </si>
+  <si>
+    <t>10.240.8.16</t>
+  </si>
+  <si>
+    <t>TGTYRPTPE01</t>
+  </si>
+  <si>
+    <t>10.240.8.17</t>
+  </si>
+  <si>
+    <t>PGCRSUBPE01</t>
+  </si>
+  <si>
+    <t>10.240.8.18</t>
+  </si>
+  <si>
+    <t>TSBGSECPE01</t>
+  </si>
+  <si>
+    <t>10.240.8.19</t>
+  </si>
+  <si>
+    <t>PSIGSECPE01</t>
+  </si>
+  <si>
+    <t>10.240.8.20</t>
+  </si>
+  <si>
+    <t>MSNGSUBPE01</t>
+  </si>
+  <si>
+    <t>10.240.8.21</t>
+  </si>
+  <si>
+    <t>RWELSUBPE01</t>
+  </si>
+  <si>
+    <t>10.240.8.22</t>
+  </si>
+  <si>
+    <t>RRLZSECPE01</t>
+  </si>
+  <si>
+    <t>10.240.8.23</t>
+  </si>
+  <si>
+    <t>TTBNSUBPE01</t>
+  </si>
+  <si>
+    <t>10.240.8.24</t>
+  </si>
+  <si>
+    <t>CMRNSUBPE01</t>
+  </si>
+  <si>
+    <t>Ip Address</t>
+  </si>
+  <si>
+    <t>AALBSUBPE01</t>
+  </si>
+  <si>
+    <t>Loopback50</t>
+  </si>
+  <si>
+    <t>ABBTRPTPE01</t>
+  </si>
+  <si>
+    <t>BLWGSUBPE01</t>
+  </si>
+  <si>
+    <t>CLBGSUBPE01</t>
+  </si>
+  <si>
+    <t>DLMNSUBPE01</t>
+  </si>
+  <si>
+    <t>EBSSSECPE01</t>
+  </si>
+  <si>
+    <t>ETONSUBPE01</t>
+  </si>
+  <si>
+    <t>KMGGSUBPE01</t>
+  </si>
+  <si>
+    <t>LCNARPTPE01</t>
+  </si>
+  <si>
+    <t>LGBASUBPE01</t>
+  </si>
+  <si>
+    <t>MLTASUBPE01</t>
+  </si>
+  <si>
+    <t>MRKNSUBPE01</t>
+  </si>
+  <si>
+    <t>NOVASUBPE01</t>
+  </si>
+  <si>
+    <t>PPNASUBPE01</t>
+  </si>
+  <si>
+    <t>PSAYSUBPE01</t>
+  </si>
+  <si>
+    <t>SCRLRPTPE01</t>
+  </si>
+  <si>
+    <t>SUNVSUBPE01</t>
+  </si>
+  <si>
+    <t>TMC2SUBPE01</t>
+  </si>
+  <si>
+    <t>URDNSUBPE01</t>
+  </si>
+  <si>
+    <t>10.240.8.26</t>
+  </si>
+  <si>
+    <t>10.240.8.25</t>
+  </si>
+  <si>
+    <t>10.240.8.27</t>
+  </si>
+  <si>
+    <t>10.240.8.28</t>
+  </si>
+  <si>
+    <t>10.240.8.29</t>
+  </si>
+  <si>
+    <t>10.240.8.30</t>
+  </si>
+  <si>
+    <t>10.240.8.31</t>
+  </si>
+  <si>
+    <t>10.240.8.32</t>
+  </si>
+  <si>
+    <t>10.240.8.35</t>
+  </si>
+  <si>
+    <t>10.240.8.33</t>
+  </si>
+  <si>
+    <t>10.240.8.36</t>
+  </si>
+  <si>
+    <t>10.240.8.37</t>
+  </si>
+  <si>
+    <t>10.240.8.38</t>
+  </si>
+  <si>
+    <t>10.240.8.39</t>
+  </si>
+  <si>
+    <t>10.240.8.40</t>
+  </si>
+  <si>
+    <t>10.240.8.41</t>
+  </si>
+  <si>
+    <t>10.240.8.42</t>
+  </si>
+  <si>
+    <t>10.240.8.34</t>
+  </si>
+  <si>
+    <t>10.240.8.43</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>OSPF Area</t>
+  </si>
+  <si>
+    <t>Grid Name</t>
+  </si>
+  <si>
+    <t>ASR903 sites</t>
+  </si>
+  <si>
+    <t>Management IP</t>
+  </si>
+  <si>
+    <t>OLD termination ASR9K</t>
+  </si>
+  <si>
+    <t>Management  IP</t>
+  </si>
+  <si>
+    <t>New termination ASR9900</t>
+  </si>
+  <si>
+    <t>OSPF 110</t>
+  </si>
+  <si>
+    <t>Kamagong - MOC (PDC)</t>
+  </si>
+  <si>
+    <t>KMGASR01 </t>
+  </si>
+  <si>
+    <t>10.228.0.8</t>
+  </si>
+  <si>
+    <t>PDCASR01</t>
+  </si>
+  <si>
+    <t>10.228.0.1</t>
+  </si>
+  <si>
+    <t>OSPF 120</t>
+  </si>
+  <si>
+    <t>Kamagong - Manila</t>
+  </si>
+  <si>
+    <t>MNLASR01 </t>
+  </si>
+  <si>
+    <t>10.228.0.9</t>
+  </si>
+  <si>
+    <t>KMGPASR9K </t>
+  </si>
+  <si>
+    <t>OSPF 130</t>
+  </si>
+  <si>
+    <t>Kamagong - Alabang</t>
+  </si>
+  <si>
+    <t>KMGASR01</t>
+  </si>
+  <si>
+    <t>ALBASR01</t>
+  </si>
+  <si>
+    <t>10.228.0.13</t>
+  </si>
+  <si>
+    <t>OSPF 140</t>
+  </si>
+  <si>
+    <t>Alabang - Pasig</t>
+  </si>
+  <si>
+    <t>PSGASR01</t>
+  </si>
+  <si>
+    <t>10.228.0.10</t>
+  </si>
+  <si>
+    <t>OSPF 150</t>
+  </si>
+  <si>
+    <t>Marikina - Rizal</t>
+  </si>
+  <si>
+    <t>MKNASR01</t>
+  </si>
+  <si>
+    <t>10.228.0.6</t>
+  </si>
+  <si>
+    <t>VLZASR01</t>
+  </si>
+  <si>
+    <t>10.228.0.5</t>
+  </si>
+  <si>
+    <t>OSPF 160</t>
+  </si>
+  <si>
+    <t>Manila - Balintawak (SDC)</t>
+  </si>
+  <si>
+    <t>MNLASR01</t>
+  </si>
+  <si>
+    <t>NPRTSUBPE01 </t>
+  </si>
+  <si>
+    <t>SDCASR01</t>
+  </si>
+  <si>
+    <t>10.228.0.2</t>
+  </si>
+  <si>
+    <t>OSPF 210</t>
+  </si>
+  <si>
+    <t>Marikina - Valenzuela</t>
+  </si>
+  <si>
+    <t>RZLASR01</t>
+  </si>
+  <si>
+    <t>10.228.0.7</t>
+  </si>
+  <si>
+    <t>MKNSUBPE01</t>
+  </si>
+  <si>
+    <t>OSPF 220</t>
+  </si>
+  <si>
+    <t>MOC (PDC) - St. Rosa</t>
+  </si>
+  <si>
+    <t>SRSASR01</t>
+  </si>
+  <si>
+    <t>10.228.0.12</t>
+  </si>
+  <si>
+    <t>New Termination ASR9K</t>
+  </si>
+  <si>
+    <t>OSPF 170 </t>
+  </si>
+  <si>
+    <t>Plaridel - Duhat</t>
+  </si>
+  <si>
+    <t>PDLASR01</t>
+  </si>
+  <si>
+    <t>10.228.0.3</t>
+  </si>
+  <si>
+    <t>DHTASR01</t>
+  </si>
+  <si>
+    <t>10.228.0.4</t>
+  </si>
+  <si>
+    <t>OSPF 180</t>
+  </si>
+  <si>
+    <t>Duhat - Balintawak (MOC)</t>
+  </si>
+  <si>
+    <t>OSPF 250</t>
+  </si>
+  <si>
+    <t>Plaridel - Baliwag</t>
+  </si>
+  <si>
+    <t>BLWGUBPE01</t>
+  </si>
+  <si>
+    <t>10.240.8/27</t>
+  </si>
+  <si>
+    <t>OSPF 190 </t>
+  </si>
+  <si>
+    <t>Cavite - Sta. Rosa 1st Grid</t>
+  </si>
+  <si>
+    <t>CVTASR01</t>
+  </si>
+  <si>
+    <t>10.228.0.11</t>
+  </si>
+  <si>
+    <t>OSPF 200</t>
+  </si>
+  <si>
+    <t>Sta. Rosa - San Pablo</t>
+  </si>
+  <si>
+    <t>EBSSECPE01</t>
+  </si>
+  <si>
+    <t>SPBASR01</t>
+  </si>
+  <si>
+    <t>10.228.0.14</t>
+  </si>
+  <si>
+    <t>OSPF 230</t>
+  </si>
+  <si>
+    <t>Cavite - Sta Rosa 2nd Grid</t>
+  </si>
+  <si>
+    <t>10.228.201.1</t>
+  </si>
+  <si>
+    <t>10.228.201.2</t>
+  </si>
+  <si>
+    <t>10.228.201.3</t>
+  </si>
+  <si>
+    <t>10.228.201.4</t>
+  </si>
+  <si>
+    <t>10.228.201.5</t>
+  </si>
+  <si>
+    <t>10.228.201.6</t>
+  </si>
+  <si>
+    <t>10.228.201.7</t>
+  </si>
+  <si>
+    <t>10.228.201.8</t>
+  </si>
+  <si>
+    <t>10.228.201.9</t>
+  </si>
+  <si>
+    <t>10.228.201.10</t>
+  </si>
+  <si>
+    <t>10.228.201.11</t>
+  </si>
+  <si>
+    <t>10.228.201.12</t>
+  </si>
+  <si>
+    <t>10.228.201.13</t>
+  </si>
+  <si>
+    <t>10.228.201.14</t>
+  </si>
+  <si>
+    <t>10.228.201.15</t>
+  </si>
+  <si>
+    <t>10.228.201.16</t>
+  </si>
+  <si>
+    <t>VPN_Data_Apps</t>
+  </si>
+  <si>
+    <t>10.0.128.1</t>
+  </si>
+  <si>
+    <t>VPN_IT_Mgt</t>
+  </si>
+  <si>
+    <t>10.167.2.1</t>
+  </si>
+  <si>
+    <t>10.170.0.1</t>
+  </si>
+  <si>
+    <t>VPN_Scada</t>
+  </si>
+  <si>
+    <t>10.160.0.11</t>
+  </si>
+  <si>
+    <t>10.160.1.11</t>
+  </si>
+  <si>
+    <t>10.160.2.12</t>
+  </si>
+  <si>
+    <t>10.180.0.1</t>
+  </si>
+  <si>
+    <t>VPN_Tetra</t>
+  </si>
+  <si>
+    <t>10.230.128.108</t>
+  </si>
+  <si>
+    <t>VPN_Transport_Mgt</t>
+  </si>
+  <si>
+    <t>10.112.6.209</t>
+  </si>
+  <si>
+    <t>VPN_Metering</t>
+  </si>
+  <si>
+    <t>172.16.64.61</t>
+  </si>
+  <si>
+    <t>172.16.66.60</t>
+  </si>
+  <si>
+    <t>VPN_WPN</t>
+  </si>
+  <si>
+    <t>10.111.30.17</t>
+  </si>
+  <si>
+    <t>10.111.30.18</t>
+  </si>
+  <si>
+    <t>10.111.30.19</t>
+  </si>
+  <si>
+    <t>10.111.30.20</t>
+  </si>
+  <si>
+    <t>10.111.30.21</t>
+  </si>
+  <si>
+    <t>route visible via VPN_Data_Apps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No route received </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -258,8 +1109,22 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -282,6 +1147,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF366092"/>
+        <bgColor rgb="FF366092"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -312,7 +1189,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -328,6 +1205,46 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1027,5 +1944,2188 @@
   <autoFilter ref="A1:E23" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter>
+    <oddFooter>&amp;R_x000D_&amp;1#&amp;"Aptos"&amp;8&amp;K000000 Cisco Confidential</oddFooter>
+  </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46773A2C-A366-4CBE-8F86-2BA9A5723480}">
+  <dimension ref="A1:K26"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="49.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="23" t="s">
+        <v>130</v>
+      </c>
+      <c r="C1" s="23" t="s">
+        <v>131</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>132</v>
+      </c>
+      <c r="E1" s="23" t="s">
+        <v>133</v>
+      </c>
+      <c r="F1" s="24" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="B2" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="C2" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="E2" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2" s="22" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="F3" s="22" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="E4" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="F4" s="22" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="D5" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="E5" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="F5" s="22" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="E6" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="F6" s="22" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="D7" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="E7" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="F7" s="22" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="E8" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="F8" s="22" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="D9" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="E9" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="F9" s="22" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="B10" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="D10" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="E10" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="F10" s="22" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="B11" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="D11" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="E11" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="F11" s="22" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="B12" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="D12" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="E12" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="F12" s="22" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="B13" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="D13" s="21" t="s">
+        <v>97</v>
+      </c>
+      <c r="E13" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="F13" s="22" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="B14" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="D14" s="21" t="s">
+        <v>100</v>
+      </c>
+      <c r="E14" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="F14" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="B15" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="D15" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="E15" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="F15" s="22" t="s">
+        <v>310</v>
+      </c>
+      <c r="K15">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="B16" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="D16" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="E16" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="F16" s="22" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="B17" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="D17" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="E17" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="F17" s="22" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="B18" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="C18" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="D18" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="E18" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="F18" s="12"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="20" t="s">
+        <v>113</v>
+      </c>
+      <c r="B19" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="C19" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="D19" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="E19" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="F19" s="12"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="B20" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="C20" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="D20" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="E20" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="F20" s="12"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="B21" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="C21" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="D21" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="E21" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="F21" s="12"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="B22" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="C22" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="D22" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="E22" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="F22" s="12"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="B23" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="C23" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="D23" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="E23" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="F23" s="12"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="B24" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="C24" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="D24" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="E24" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="F24" s="12"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="20" t="s">
+        <v>125</v>
+      </c>
+      <c r="B25" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="C25" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="D25" s="20" t="s">
+        <v>126</v>
+      </c>
+      <c r="E25" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="F25" s="12"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="B26" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="C26" s="20"/>
+      <c r="D26" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="E26" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="F26" s="12"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddFooter>&amp;R_x000D_&amp;1#&amp;"Aptos"&amp;8&amp;K000000 Cisco Confidential</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98DD2DDA-F1C8-4934-A02E-F06226CD5A2E}">
+  <dimension ref="A1:C44"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="C29" s="12" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="B31" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="C31" s="12" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="B32" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="C32" s="12" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="B33" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="C33" s="12" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="B34" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="C34" s="12" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="B35" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="B36" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="C36" s="12" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="B37" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="C37" s="12" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="C38" s="12" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="B39" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="C39" s="12" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="B40" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="C40" s="12" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="B41" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="C41" s="12" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="B42" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="C42" s="12" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="B43" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="C43" s="12" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="B44" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="C44" s="12" t="s">
+        <v>160</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35E5E706-A42C-4968-A1EE-586A3D93A41D}">
+  <dimension ref="A1:I48"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" style="19"/>
+    <col min="2" max="2" width="15.28515625" customWidth="1"/>
+    <col min="3" max="3" width="21.42578125" customWidth="1"/>
+    <col min="4" max="4" width="18.42578125" customWidth="1"/>
+    <col min="5" max="5" width="16.85546875" customWidth="1"/>
+    <col min="6" max="6" width="18.28515625" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1"/>
+    <col min="8" max="8" width="19.85546875" customWidth="1"/>
+    <col min="9" max="9" width="16.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="F1" s="16" t="s">
+        <v>229</v>
+      </c>
+      <c r="G1" s="16" t="s">
+        <v>230</v>
+      </c>
+      <c r="H1" s="16" t="s">
+        <v>231</v>
+      </c>
+      <c r="I1" s="16" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="18">
+        <v>1</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>232</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>233</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="F2" s="15" t="s">
+        <v>234</v>
+      </c>
+      <c r="G2" s="15" t="s">
+        <v>235</v>
+      </c>
+      <c r="H2" s="15" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="18"/>
+      <c r="B3" s="14"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="15" t="s">
+        <v>204</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>223</v>
+      </c>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="15"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="18"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="15"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="18"/>
+      <c r="B5" s="14"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="F5" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="G5" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="H5" s="15" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="18">
+        <v>2</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>238</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>239</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>153</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="F6" s="15" t="s">
+        <v>240</v>
+      </c>
+      <c r="G6" s="15" t="s">
+        <v>241</v>
+      </c>
+      <c r="H6" s="15" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="18"/>
+      <c r="B7" s="14"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>158</v>
+      </c>
+      <c r="F7" s="15"/>
+      <c r="G7" s="15"/>
+      <c r="H7" s="15"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="18"/>
+      <c r="B8" s="14"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="15" t="s">
+        <v>193</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>212</v>
+      </c>
+      <c r="F8" s="15" t="s">
+        <v>234</v>
+      </c>
+      <c r="G8" s="15" t="s">
+        <v>235</v>
+      </c>
+      <c r="H8" s="15" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="18">
+        <v>3</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>243</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>244</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>219</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>245</v>
+      </c>
+      <c r="G9" s="15" t="s">
+        <v>235</v>
+      </c>
+      <c r="H9" s="15" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="18"/>
+      <c r="B10" s="14"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>168</v>
+      </c>
+      <c r="F10" s="14"/>
+      <c r="G10" s="14"/>
+      <c r="H10" s="15"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="18"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="F11" s="14"/>
+      <c r="G11" s="14"/>
+      <c r="H11" s="15"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="18"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="15" t="s">
+        <v>199</v>
+      </c>
+      <c r="E12" s="15" t="s">
+        <v>218</v>
+      </c>
+      <c r="F12" s="15" t="s">
+        <v>246</v>
+      </c>
+      <c r="G12" s="15" t="s">
+        <v>247</v>
+      </c>
+      <c r="H12" s="15" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="18">
+        <v>4</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>249</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>173</v>
+      </c>
+      <c r="E13" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="F13" s="15" t="s">
+        <v>250</v>
+      </c>
+      <c r="G13" s="15" t="s">
+        <v>251</v>
+      </c>
+      <c r="H13" s="15" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="18"/>
+      <c r="B14" s="14"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="15" t="s">
+        <v>202</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>221</v>
+      </c>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="15"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="18"/>
+      <c r="B15" s="14"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="15"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="18"/>
+      <c r="B16" s="14"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="15" t="s">
+        <v>185</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>246</v>
+      </c>
+      <c r="G16" s="15" t="s">
+        <v>247</v>
+      </c>
+      <c r="H16" s="15" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="18">
+        <v>5</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>252</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>253</v>
+      </c>
+      <c r="D17" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="F17" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="G17" s="15" t="s">
+        <v>255</v>
+      </c>
+      <c r="H17" s="15" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="18"/>
+      <c r="B18" s="14"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="E18" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="F18" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="G18" s="15" t="s">
+        <v>257</v>
+      </c>
+      <c r="H18" s="15" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="18">
+        <v>6</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>258</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>259</v>
+      </c>
+      <c r="D19" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="E19" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="F19" s="15" t="s">
+        <v>260</v>
+      </c>
+      <c r="G19" s="15" t="s">
+        <v>241</v>
+      </c>
+      <c r="H19" s="15" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="18"/>
+      <c r="B20" s="14"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="15" t="s">
+        <v>181</v>
+      </c>
+      <c r="E20" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="F20" s="14"/>
+      <c r="G20" s="14"/>
+      <c r="H20" s="15"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="18"/>
+      <c r="B21" s="14"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="15" t="s">
+        <v>261</v>
+      </c>
+      <c r="E21" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="F21" s="14"/>
+      <c r="G21" s="14"/>
+      <c r="H21" s="15"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="18"/>
+      <c r="B22" s="14"/>
+      <c r="C22" s="14"/>
+      <c r="D22" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="E22" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="F22" s="15" t="s">
+        <v>262</v>
+      </c>
+      <c r="G22" s="15" t="s">
+        <v>263</v>
+      </c>
+      <c r="H22" s="15" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="18">
+        <v>7</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>264</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>265</v>
+      </c>
+      <c r="D23" s="15" t="s">
+        <v>196</v>
+      </c>
+      <c r="E23" s="15" t="s">
+        <v>215</v>
+      </c>
+      <c r="F23" s="15" t="s">
+        <v>266</v>
+      </c>
+      <c r="G23" s="15" t="s">
+        <v>267</v>
+      </c>
+      <c r="H23" s="15" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="18"/>
+      <c r="B24" s="14"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="E24" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="15"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="18"/>
+      <c r="B25" s="14"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="15" t="s">
+        <v>190</v>
+      </c>
+      <c r="E25" s="15" t="s">
+        <v>209</v>
+      </c>
+      <c r="F25" s="14"/>
+      <c r="G25" s="14"/>
+      <c r="H25" s="15"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="18"/>
+      <c r="B26" s="14"/>
+      <c r="C26" s="14"/>
+      <c r="D26" s="15" t="s">
+        <v>268</v>
+      </c>
+      <c r="E26" s="15" t="s">
+        <v>216</v>
+      </c>
+      <c r="F26" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="G26" s="15" t="s">
+        <v>255</v>
+      </c>
+      <c r="H26" s="15" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="18">
+        <v>8</v>
+      </c>
+      <c r="B27" s="14" t="s">
+        <v>269</v>
+      </c>
+      <c r="C27" s="14" t="s">
+        <v>270</v>
+      </c>
+      <c r="D27" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="E27" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="F27" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="G27" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="H27" s="15" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="18"/>
+      <c r="B28" s="14"/>
+      <c r="C28" s="14"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="15" t="s">
+        <v>271</v>
+      </c>
+      <c r="G28" s="15" t="s">
+        <v>272</v>
+      </c>
+      <c r="H28" s="15" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A30" s="13" t="s">
+        <v>224</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>225</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>226</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>227</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>228</v>
+      </c>
+      <c r="F30" s="13" t="s">
+        <v>229</v>
+      </c>
+      <c r="G30" s="13" t="s">
+        <v>228</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="18">
+        <v>9</v>
+      </c>
+      <c r="B31" s="14" t="s">
+        <v>274</v>
+      </c>
+      <c r="C31" s="14" t="s">
+        <v>275</v>
+      </c>
+      <c r="D31" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="E31" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="F31" s="15" t="s">
+        <v>276</v>
+      </c>
+      <c r="G31" s="15" t="s">
+        <v>277</v>
+      </c>
+      <c r="H31" s="15" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="18"/>
+      <c r="B32" s="14"/>
+      <c r="C32" s="14"/>
+      <c r="D32" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="E32" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="F32" s="15" t="s">
+        <v>278</v>
+      </c>
+      <c r="G32" s="15" t="s">
+        <v>279</v>
+      </c>
+      <c r="H32" s="15" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="18">
+        <v>10</v>
+      </c>
+      <c r="B33" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="C33" s="14" t="s">
+        <v>281</v>
+      </c>
+      <c r="D33" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="E33" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="F33" s="15" t="s">
+        <v>278</v>
+      </c>
+      <c r="G33" s="15" t="s">
+        <v>279</v>
+      </c>
+      <c r="H33" s="15" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="18"/>
+      <c r="B34" s="14"/>
+      <c r="C34" s="14"/>
+      <c r="D34" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="E34" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="F34" s="15"/>
+      <c r="G34" s="15"/>
+      <c r="H34" s="15"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="18"/>
+      <c r="B35" s="14"/>
+      <c r="C35" s="14"/>
+      <c r="D35" s="15" t="s">
+        <v>192</v>
+      </c>
+      <c r="E35" s="15" t="s">
+        <v>211</v>
+      </c>
+      <c r="F35" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="G35" s="15" t="s">
+        <v>255</v>
+      </c>
+      <c r="H35" s="15" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="13">
+        <v>11</v>
+      </c>
+      <c r="B36" s="15" t="s">
+        <v>282</v>
+      </c>
+      <c r="C36" s="15" t="s">
+        <v>283</v>
+      </c>
+      <c r="D36" s="15" t="s">
+        <v>284</v>
+      </c>
+      <c r="E36" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="F36" s="15" t="s">
+        <v>276</v>
+      </c>
+      <c r="G36" s="15" t="s">
+        <v>277</v>
+      </c>
+      <c r="H36" s="15" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A38" s="13" t="s">
+        <v>224</v>
+      </c>
+      <c r="B38" s="13" t="s">
+        <v>225</v>
+      </c>
+      <c r="C38" s="13" t="s">
+        <v>226</v>
+      </c>
+      <c r="D38" s="13" t="s">
+        <v>227</v>
+      </c>
+      <c r="E38" s="13" t="s">
+        <v>228</v>
+      </c>
+      <c r="F38" s="13" t="s">
+        <v>229</v>
+      </c>
+      <c r="G38" s="13" t="s">
+        <v>228</v>
+      </c>
+      <c r="H38" s="13" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" s="18">
+        <v>12</v>
+      </c>
+      <c r="B39" s="14" t="s">
+        <v>286</v>
+      </c>
+      <c r="C39" s="14" t="s">
+        <v>287</v>
+      </c>
+      <c r="D39" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="E39" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="F39" s="15" t="s">
+        <v>288</v>
+      </c>
+      <c r="G39" s="15" t="s">
+        <v>289</v>
+      </c>
+      <c r="H39" s="15" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" s="18"/>
+      <c r="B40" s="14"/>
+      <c r="C40" s="14"/>
+      <c r="D40" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="E40" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="F40" s="15"/>
+      <c r="G40" s="15"/>
+      <c r="H40" s="15"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" s="18"/>
+      <c r="B41" s="14"/>
+      <c r="C41" s="14"/>
+      <c r="D41" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="E41" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="F41" s="15" t="s">
+        <v>271</v>
+      </c>
+      <c r="G41" s="15" t="s">
+        <v>272</v>
+      </c>
+      <c r="H41" s="15" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" s="18">
+        <v>13</v>
+      </c>
+      <c r="B42" s="17" t="s">
+        <v>290</v>
+      </c>
+      <c r="C42" s="14" t="s">
+        <v>291</v>
+      </c>
+      <c r="D42" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="E42" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="F42" s="15" t="s">
+        <v>271</v>
+      </c>
+      <c r="G42" s="15" t="s">
+        <v>272</v>
+      </c>
+      <c r="H42" s="15" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" s="18"/>
+      <c r="B43" s="17"/>
+      <c r="C43" s="14"/>
+      <c r="D43" s="15" t="s">
+        <v>292</v>
+      </c>
+      <c r="E43" s="15" t="s">
+        <v>210</v>
+      </c>
+      <c r="F43" s="14"/>
+      <c r="G43" s="14"/>
+      <c r="H43" s="14"/>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="18"/>
+      <c r="B44" s="17"/>
+      <c r="C44" s="14"/>
+      <c r="D44" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="E44" s="15" t="s">
+        <v>208</v>
+      </c>
+      <c r="F44" s="14"/>
+      <c r="G44" s="14"/>
+      <c r="H44" s="14"/>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="18"/>
+      <c r="B45" s="17"/>
+      <c r="C45" s="14"/>
+      <c r="D45" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="E45" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="F45" s="15" t="s">
+        <v>293</v>
+      </c>
+      <c r="G45" s="15" t="s">
+        <v>294</v>
+      </c>
+      <c r="H45" s="15" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="18">
+        <v>14</v>
+      </c>
+      <c r="B46" s="14" t="s">
+        <v>295</v>
+      </c>
+      <c r="C46" s="14" t="s">
+        <v>296</v>
+      </c>
+      <c r="D46" s="15" t="s">
+        <v>187</v>
+      </c>
+      <c r="E46" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="F46" s="15" t="s">
+        <v>288</v>
+      </c>
+      <c r="G46" s="15" t="s">
+        <v>289</v>
+      </c>
+      <c r="H46" s="15" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" s="18"/>
+      <c r="B47" s="14"/>
+      <c r="C47" s="14"/>
+      <c r="D47" s="15" t="s">
+        <v>203</v>
+      </c>
+      <c r="E47" s="15" t="s">
+        <v>222</v>
+      </c>
+      <c r="F47" s="15"/>
+      <c r="G47" s="15"/>
+      <c r="H47" s="15"/>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" s="18"/>
+      <c r="B48" s="14"/>
+      <c r="C48" s="14"/>
+      <c r="D48" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="E48" s="15" t="s">
+        <v>214</v>
+      </c>
+      <c r="F48" s="15" t="s">
+        <v>271</v>
+      </c>
+      <c r="G48" s="15" t="s">
+        <v>272</v>
+      </c>
+      <c r="H48" s="15" t="s">
+        <v>74</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="54">
+    <mergeCell ref="A46:A48"/>
+    <mergeCell ref="B46:B48"/>
+    <mergeCell ref="C46:C48"/>
+    <mergeCell ref="A42:A45"/>
+    <mergeCell ref="B42:B45"/>
+    <mergeCell ref="C42:C45"/>
+    <mergeCell ref="F43:F44"/>
+    <mergeCell ref="G43:G44"/>
+    <mergeCell ref="H43:H44"/>
+    <mergeCell ref="A33:A35"/>
+    <mergeCell ref="B33:B35"/>
+    <mergeCell ref="C33:C35"/>
+    <mergeCell ref="A39:A41"/>
+    <mergeCell ref="B39:B41"/>
+    <mergeCell ref="C39:C41"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="E27:E28"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="G20:G21"/>
+    <mergeCell ref="A23:A26"/>
+    <mergeCell ref="B23:B26"/>
+    <mergeCell ref="C23:C26"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="A19:A22"/>
+    <mergeCell ref="B19:B22"/>
+    <mergeCell ref="C19:C22"/>
+    <mergeCell ref="A9:A12"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="C9:C12"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="A13:A16"/>
+    <mergeCell ref="B13:B16"/>
+    <mergeCell ref="C13:C16"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="B2:B5"/>
+    <mergeCell ref="C2:C5"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="A6:A8"/>
+    <mergeCell ref="B6:B8"/>
+    <mergeCell ref="C6:C8"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D647111-4141-4C12-89F7-121B6BA0571E}">
+  <dimension ref="A2:C17"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="25" t="s">
+        <v>313</v>
+      </c>
+      <c r="B2" s="26" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="25" t="s">
+        <v>315</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>316</v>
+      </c>
+      <c r="C3" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="B4" s="26" t="s">
+        <v>317</v>
+      </c>
+      <c r="C4" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="12" t="s">
+        <v>318</v>
+      </c>
+      <c r="B5" s="26" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="12" t="s">
+        <v>318</v>
+      </c>
+      <c r="B6" s="26" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="12" t="s">
+        <v>318</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="12" t="s">
+        <v>318</v>
+      </c>
+      <c r="B8" s="26" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="12" t="s">
+        <v>323</v>
+      </c>
+      <c r="B9" s="26" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="12" t="s">
+        <v>325</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="26" t="s">
+        <v>327</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="26" t="s">
+        <v>327</v>
+      </c>
+      <c r="B12" s="26" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="26" t="s">
+        <v>330</v>
+      </c>
+      <c r="B13" s="26" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="26" t="s">
+        <v>330</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="26" t="s">
+        <v>330</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="26" t="s">
+        <v>330</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="26" t="s">
+        <v>330</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>335</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{c8f49a32-fde3-48a5-9266-b5b0972a22dc}" enabled="1" method="Standard" siteId="{5ae1af62-9505-4097-a69a-c1553ef7840e}" removed="0"/>
+</clbl:labelList>
 </file>